--- a/Tests/excel/module08_test_cases.xlsx
+++ b/Tests/excel/module08_test_cases.xlsx
@@ -1293,40 +1293,40 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Tải lên ảnh đại diện hợp lệ định dạng JPG</t>
+          <t>Upload valid profile photo in JPG format</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải lên ảnh đại diện định dạng JPG thành công và cập nhật vào thông tin học sinh.</t>
+          <t>Verify functionality for tai len profile photo format JPG successfully va cap nhat vao thong tin student.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở trang Chi tiết Học sinh (Student Detail) của một học sinh chưa có ảnh đại diện (đang hiển thị ảnh mặc định).</t>
+          <t>User is logged in as Staff.
+Currently on Student Detail page of a student without profile photo (displaying default photo).</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg (kích thước &lt; 2MB)</t>
+          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg (kich thuoc &lt; 2MB)</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn biểu tượng tải ảnh đại diện.
-3. Chọn file student_avatar.jpg từ thiết bị.
-4. Quan sát ảnh xem trước hiển thị trên màn hình.
-5. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select bieu tuong tai profile photo.
+3. Select file student_avatar.jpg tu thiet bi.
+4. Observe preview photo display tren man hinh.
+5. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tải lên thành công.
-Ảnh xem trước hiển thị tức thì trên giao diện trước khi lưu.
-Sau khi lưu, thông tin học sinh được cập nhật: ảnh đại diện hiển thị kiểu hình tròn tại Sidebar chi tiết (200x200 px) và danh sách học sinh (52x52 px).
-File ảnh được lưu trên Google Drive dưới tên "Nguyen_Van_A_{Timestamp}.jpg" với quyền xem "Anyone with the link".</t>
+          <t>System display notification tai len successfully.
+Anh xem truoc display tuc thi tren interface truoc khi save.
+Sau khi save, thong tin student duoc cap nhat: profile photo display kieu hinh tron tai Sidebar chi tiet (200x200 px) va danh sach student (52x52 px).
+File photo duoc save tren Google Drive duoi ten "Nguyen_Van_A_{Timestamp}.jpg" voi quyen xem "Anyone with the link".</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F01, Rule 5.2, Google Drive Integration (Mục 7)</t>
+          <t>Related to M08-F01, Rule 5.2, Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -1369,18 +1369,18 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Tải lên ảnh đại diện hợp lệ định dạng PNG</t>
+          <t>Upload valid profile photo in PNG format</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tải lên ảnh đại diện định dạng PNG thành công và cập nhật vào thông tin học sinh.</t>
+          <t>Verify functionality for tai len profile photo format PNG successfully va cap nhat vao thong tin student.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở trang Chi tiết Học sinh (Student Detail) của một học sinh chưa có ảnh đại diện.</t>
+          <t>User is logged in as Staff.
+Currently on Student Detail page of a student without profile photo.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26002 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn biểu tượng tải ảnh đại diện.
-3. Chọn file student_avatar2.png.
-4. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Select student PNV26002 va mo trang Chi tiet Hoc sinh.
+2. Nhap select bieu tuong tai profile photo.
+3. Select file student_avatar2.png.
+4. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo tải lên thành công.
-Ảnh đại diện PNG hiển thị chính xác kiểu hình tròn ở tất cả các vị trí.
-File ảnh được tải lên Google Drive và được đặt tên theo định dạng {StudentName}_{Timestamp}.jpg.</t>
+          <t>System display notification tai len successfully.
+Anh dai dien PNG display chinh xac kieu hinh tron o tat ca cac vi tri.
+File photo duoc tai len Google Drive va duoc dat ten theo format {StudentName}_{Timestamp}.jpg.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F01, Rule 5.2</t>
+          <t>Related to M08-F01, Rule 5.2</t>
         </is>
       </c>
     </row>
@@ -1443,18 +1443,18 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Thay thế ảnh đại diện hiện tại</t>
+          <t>Replace current profile photo</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Xác minh khi tải lên ảnh đại diện mới, hệ thống tự động cập nhật thông tin học sinh và xóa file ảnh cũ trên Google Drive.</t>
+          <t>Verify khi tai len new profile photo, system tu dong cap nhat thong tin student va delete file old photo tren Google Drive.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có sẵn ảnh đại diện cũ trên hệ thống và Google Drive.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co san old profile photo tren system va Google Drive.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn tải ảnh đại diện mới.
-3. Chọn file new_avatar.jpg.
-4. Nhấn nút "Lưu" (Save).
-5. Kiểm tra thư mục lưu trữ trên Google Drive.</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select tai new profile photo.
+3. Select file new_avatar.jpg.
+4. Nhan nut "Save" (Save).
+5. Verify thu muc archive tren Google Drive.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo thay thế thành công.
-Ảnh đại diện mới hiển thị trên hệ thống.
-File ảnh cũ của học sinh PNV26001 trên Google Drive bị xóa hoàn toàn khỏi thư mục lưu trữ (không giữ lại file cũ).
-Chỉ còn lại file ảnh mới trên Google Drive.</t>
+          <t>System display notification replace successfully.
+Anh dai dien moi display tren system.
+File old photo cua student PNV26001 tren Google Drive bi delete hoan toan khoi thu muc archive (khong giu lai file cu).
+Chi con lai file new photo tren Google Drive.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F02, Rule 5.3</t>
+          <t>Related to M08-F02, Rule 5.3</t>
         </is>
       </c>
     </row>
@@ -1519,18 +1519,18 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Xóa ảnh đại diện hiện tại (Soft Delete)</t>
+          <t>Delete current profile photo (Soft Delete)</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng xóa ảnh đại diện của học sinh, chuyển file cũ vào Google Drive Trash và hiển thị avatar mặc định.</t>
+          <t>Verify functionality for delete profile photo cua student, chuyen file cu vao Google Drive Trash va display avatar mac dinh.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có sẵn ảnh đại diện trên hệ thống.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co san profile photo tren system.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1540,18 +1540,18 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001 và mở trang Chi tiết Học sinh.
-2. Nhấp chọn nút "Xóa ảnh" (Remove Photo).
-3. Xác nhận xóa khi hệ thống hiển thị hộp thoại xác nhận.
-4. Nhấn nút "Lưu" (Save).
-5. Kiểm tra Google Drive Trash.</t>
+          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
+2. Nhap select nut "Delete photo" (Remove Photo).
+3. Xac nhan delete khi system display hop thoai xac nhan.
+4. Nhan nut "Save" (Save).
+5. Verify Google Drive Trash.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Ảnh đại diện cũ của học sinh bị xóa khỏi giao diện.
-Hệ thống hiển thị ảnh đại diện mặc định (chữ cái viết tắt tên học sinh).
-Trên Google Drive, file ảnh cũ của học sinh được di chuyển vào thùng rác (Drive Trash) chứ không bị xóa vĩnh viễn ngay lập tức.</t>
+          <t>Anh dai dien cu cua student bi delete khoi interface.
+System display profile photo mac dinh (initials ten student).
+Tren Google Drive, file old photo cua student duoc di chuyen vao trash (Drive Trash) chu khong bi permanently deleted ngay lap tuc.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F03, Rule 5.4</t>
+          <t>Related to M08-F03, Rule 5.4</t>
         </is>
       </c>
     </row>
@@ -1594,18 +1594,18 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Hiển thị avatar mặc định khi học sinh chưa có ảnh đại diện</t>
+          <t>Hien thi avatar mac dinh khi student chua co profile photo</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống hiển thị ảnh đại diện mặc định là 2 chữ cái đầu của tên học sinh khi không có ảnh.</t>
+          <t>Verify system display profile photo mac dinh la 2 initials cua ten student khi khong co photo.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh "Nguyen Van A" chưa tải ảnh đại diện lên hệ thống.</t>
+          <t>User is logged in as Staff.
+Hoc sinh "Nguyen Van A" chua tai profile photo len system.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -1615,16 +1615,16 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Vào danh sách học sinh.
-2. Tìm học sinh "Nguyen Van A".
-3. Quan sát ảnh đại diện hiển thị bên cạnh tên học sinh.
-4. Kiểm tra tại trang Chi tiết học sinh và màn hình Home Dashboard.</t>
+          <t>1. Vao danh sach student.
+2. Tim student "Nguyen Van A".
+3. Observe profile photo display ben canh ten student.
+4. Verify tai trang Chi tiet student va man hinh Home Dashboard.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống tự động hiển thị ảnh đại diện dạng hình tròn chứa 2 chữ cái viết tắt là "NA" (chữ cái đầu của Tên và Họ).
-Ảnh mặc định này hiển thị đồng bộ ở cả danh sách học sinh và chi tiết học sinh.</t>
+          <t>System tu dong display profile photo dang hinh tron chua 2 initials la "NA" (initials cua Ten va Ho).
+Anh mac dinh nay display dong bo o ca danh sach student va chi tiet student.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F04, Rule 5.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
+          <t>Related to M08-F04, Rule 5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TC-M08-006</t>
@@ -1667,18 +1667,18 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra kích thước hiển thị ảnh đại diện ở các vị trí khác nhau</t>
+          <t>Verify kich thuoc display profile photo o cac vi tri khac nhau</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Xác minh ảnh đại diện hiển thị đúng kích thước cấu hình và đúng định dạng hình tròn ở mọi màn hình.</t>
+          <t>Verify profile photo display dung kich thuoc cau hinh va dung format hinh tron o moi man hinh.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26001 đã có ảnh đại diện hợp lệ.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26001 da co profile photo hop le.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1688,18 +1688,18 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Xem ảnh học sinh tại danh sách học sinh.
-2. Nhấp xem chi tiết học sinh PNV26001 và quan sát Sidebar.
-3. Mở Dialog chỉnh sửa thông tin học sinh.
-4. Về màn hình Home Dashboard và tìm ảnh đại diện học sinh đó.</t>
+          <t>1. Xem photo student tai danh sach student.
+2. Nhap xem chi tiet student PNV26001 va observe Sidebar.
+3. Mo Dialog edit thong tin student.
+4. Ve man hinh Home Dashboard va tim profile photo student do.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Ảnh đại diện hiển thị dưới dạng hình tròn với kích thước chuẩn:
-- Danh sách học sinh: 52 x 52 px
-- Dialog chỉnh sửa học sinh: 120 x 120 px
-- Sidebar chi tiết học sinh: 200 x 200 px
+          <t>Anh dai dien display as hinh tron voi kich thuoc chuan:
+- Danh sach student: 52 x 52 px
+- Dialog edit student: 120 x 120 px
+- Sidebar chi tiet student: 200 x 200 px
 - Home Dashboard: 52 x 52 px</t>
         </is>
       </c>
@@ -1716,11 +1716,11 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Display Locations (Mục 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="105" customHeight="1">
+          <t>Related to Display Locations (Section 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-M08-007</t>
@@ -1743,18 +1743,18 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Nhấn Lưu ảnh đại diện khi chưa chọn file ảnh</t>
+          <t>Nhan Save profile photo khi chua select file photo</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi người dùng cố tình lưu ảnh mà chưa chọn tệp tin nào.</t>
+          <t>Verify system bao error khi user co tinh save photo ma chua select tep tin nao.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở trang Chi tiết Học sinh của một học sinh chưa có ảnh.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo trang Chi tiet Hoc sinh cua mot student chua co photo.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1764,16 +1764,16 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001.
-2. Kích hoạt chế độ tải ảnh đại diện.
-3. Không chọn bất kỳ file nào từ thiết bị.
-4. Nhấn nút "Lưu" (Save) hoặc nút xác nhận tải lên.</t>
+          <t>1. Select student PNV26001.
+2. Kich hoat che do tai profile photo.
+3. Khong select bat ky file nao tu thiet bi.
+4. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị cảnh báo lỗi yêu cầu chọn tệp tin hình ảnh (ví dụ: "Image file is required" hoặc tương đương).
-Không có bất kỳ thay đổi nào được thực hiện.</t>
+          <t>System display cphoto bao error requires select tep tin hinh photo (e.g.: "Image file is required" hoac tuong duong).
+Khong co bat ky thay doi nao duoc thuc hien.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8)</t>
+          <t>Related to Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -1816,18 +1816,18 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Tải lên file không phải định dạng hình ảnh</t>
+          <t>Upload file not format hinh photo</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống chặn tải lên các tệp tin có định dạng không phải là ảnh (như .pdf, .docx, .txt).</t>
+          <t>Verify system chan tai len cac tep tin co format is not a photo (nhu .pdf, .docx, .txt).</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang mở trang Chi tiết Học sinh.</t>
+          <t>User is logged in as Staff.
+Dang mo trang Chi tiet Hoc sinh.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1837,16 +1837,16 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26001.
-2. Nhấp tải ảnh đại diện và chọn file document.pdf.
-3. Nhấn nút "Lưu" (Save) hoặc nút xác nhận tải lên.</t>
+          <t>1. Select student PNV26001.
+2. Nhap tai profile photo va select file document.pdf.
+3. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống không chấp nhận file PDF.
-Hiển thị thông báo lỗi yêu cầu tệp tin hình ảnh hợp lệ (ví dụ: "Invalid file format. Please upload JPG or PNG image").
-Không cho phép lưu tệp tin này làm ảnh đại diện.</t>
+          <t>System khong chap nhan file PDF.
+Hien thi notification error requires tep tin hinh photo hop le (e.g.: "Invalid file format. Please upload JPG or PNG image").
+Khong allows save tep tin nay lam profile photo.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8)</t>
+          <t>Related to Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -1889,18 +1889,18 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Xác minh cấu trúc tên file lưu trên Google Drive</t>
+          <t>Verify cau truc ten file save tren Google Drive</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo file ảnh tải lên được đổi tên theo đúng định dạng {StudentName}_{Timestamp}.jpg.</t>
+          <t>Dam bao file photo tai len duoc doi ten theo dung format {StudentName}_{Timestamp}.jpg.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Học sinh tên "John Smith" chưa có ảnh.</t>
+          <t>Nguoi dung log in quyen Staff.
+Hoc sinh ten "John Smith" chua co photo.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1910,16 +1910,16 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh "John Smith" và tải lên ảnh avatar.jpg.
-2. Nhấn "Lưu" (Save).
-3. Đăng nhập vào tài khoản Google Drive quản trị, mở thư mục lưu trữ cấu hình.
-4. Tìm kiếm file ảnh mới tải lên và kiểm tra tên file.</t>
+          <t>1. Select student "John Smith" va tai len photo avatar.jpg.
+2. Nhan "Save" (Save).
+3. Log in vao account Google Drive quan tri, mo thu muc archive cau hinh.
+4. Tim kiem file new photo tai len va kiem tra ten file.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>File ảnh được lưu trữ trên Google Drive có tên chính xác là "John_Smith_YYYYMMDDHHMMSS.jpg" (trong đó YYYYMMDDHHMMSS là thời gian lúc tải lên).
-Định dạng file được chuẩn hóa thành đuôi mở rộng .jpg.</t>
+          <t>File photo duoc archive tren Google Drive co ten chinh xac la "John_Smith_YYYYMMDDHHMMSS.jpg" (trong do YYYYMMDDHHMMSS la period luc tai len).
+Dinh dang file duoc chuan hoa thanh duoi mo rong .jpg.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -1962,36 +1962,36 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Tải lên ảnh cho học sinh có tên chứa ký tự tiếng Việt có dấu</t>
+          <t>Upload photo cho student co ten chua ky tu tieng Viet co dau</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tên file trên Google Drive có được xử lý chuẩn hóa ký tự tiếng Việt có dấu và khoảng trắng hay không.</t>
+          <t>Verify whether ten file tren Google Drive co duoc xu ly chuan hoa ky tu tieng Viet co dau va khoang trang hay khong.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Có học sinh tên "Nguyễn Hoàng Nam".</t>
+          <t>Nguoi dung log in quyen Staff.
+Co student ten "Nguyen Hoang Nam".</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Hoàng Nam"; ImageFile=avatar.jpg</t>
+          <t>StudentName="Nguyen Hoang Nam"; ImageFile=avatar.jpg</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Mở trang chi tiết học sinh "Nguyễn Hoàng Nam" và tải lên ảnh đại diện.
-2. Nhấn "Lưu".
-3. Mở Google Drive kiểm tra tên file ảnh vừa tạo.</t>
+          <t>1. Mo trang chi tiet student "Nguyen Hoang Nam" va tai len profile photo.
+2. Nhan "Save".
+3. Mo Google Drive kiem tra ten file photo vua create.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>File ảnh được tải lên thành công.
-Tên file trên Google Drive được chuẩn hóa (ví dụ chuyển thành "Nguyen_Hoang_Nam_{Timestamp}.jpg" hoặc giữ nguyên ký tự tiếng Việt có dấu nhưng khoảng trắng thay bằng gạch dưới và không bị lỗi hiển thị/mã hóa ký tự).</t>
+          <t>File photo duoc tai len successfully.
+Ten file tren Google Drive duoc chuan hoa (e.g. chuyen thanh "Nguyen_Hoang_Nam_{Timestamp}.jpg" hoac giu nguyen ky tu tieng Viet co dau nhung khoang trang thay bang gach duoi va khong bi error display/ma hoa ky tu).</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2007,11 +2007,11 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="120" customHeight="1">
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-M08-011</t>
@@ -2034,18 +2034,18 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Xác minh quyền truy cập tệp tin (File Permission) trên Google Drive</t>
+          <t>Verify quyen access tep tin (File Permission) tren Google Drive</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo tệp tin ảnh tải lên được cấu hình quyền chia sẻ công khai ở chế độ chỉ xem để hệ thống hiển thị được.</t>
+          <t>Dam bao tep tin photo tai len duoc cau hinh quyen chia se cong khai o che do chi xem de system display duoc.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Tải ảnh lên cho học sinh PNV26001 thành công.</t>
+          <t>Nguoi dung log in quyen Staff.
+Tai photo len cho student PNV26001 successfully.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2055,14 +2055,14 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Mở tài khoản Google Drive quản trị, tìm file ảnh của học sinh PNV26001 vừa tải lên.
-2. Nhấp chuột phải chọn "Chia sẻ" (Share) -&gt; "Nhận liên kết" (Get link).
-3. Kiểm tra cài đặt quyền truy cập chung.</t>
+          <t>1. Mo account Google Drive quan tri, tim file photo cua student PNV26001 vua tai len.
+2. Nhap chuot phai select "Chia se" (Share) -&gt; "Nhan lien ket" (Get link).
+3. Verify cai dat quyen access chung.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Quyền truy cập chung của file được thiết lập là "Bất kỳ ai có liên kết này" (Anyone with the link) và vai trò được gán là "Người xem" (Viewer / View only).</t>
+          <t>Quyen access chung cua file duoc thiet lap la "Bat ky ai co lien ket nay" (Anyone with the link) va vai tro duoc gan la "Nguoi xem" (Viewer / View only).</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Storage Information (Mục 3), Google Drive Integration (Mục 7)</t>
+          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
         </is>
       </c>
     </row>
@@ -2105,34 +2105,34 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Tải lên ảnh có dung lượng lớn</t>
+          <t>Upload photo co size lon</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra phản hồi của hệ thống khi cố gắng tải lên một hình ảnh có kích thước tệp tin lớn.</t>
+          <t>Verify phan hoi cua system khi co gang tai len mot hinh photo co kich thuoc tep tin lon.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở giao diện tải ảnh đại diện.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo interface tai profile photo.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=large_photo.jpg (dung lượng 15MB)</t>
+          <t>StudentCode=PNV26001; ImageFile=large_photo.jpg (size 15MB)</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Tải lên tệp tin large_photo.jpg dung lượng 15MB.
-2. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Upload tep tin large_photo.jpg size 15MB.
+2. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống tải lên thành công nếu không cấu hình giới hạn kích thước, HOẶC nếu hệ thống có giới hạn dung lượng: hiển thị thông báo lỗi yêu cầu ảnh nhỏ hơn mức quy định (ví dụ: "File size exceeds limit") và ngăn không cho tải lên.</t>
+          <t>System tai len successfully neu khong cau hinh gioi han kich thuoc, HOAC neu system co gioi han size: display notification error requires photo nho hon muc quy dinh (e.g.: "File size exceeds limit") va ngan khong cho tai len.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Test Data Preparation (Mục 11 - Large image)</t>
+          <t>Related to Test Data Preparation (Section 11 - Large image)</t>
         </is>
       </c>
     </row>
@@ -2175,18 +2175,18 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Tải lên hình ảnh có phần mở rộng viết hoa (.JPG / .PNG)</t>
+          <t>Upload hinh photo co phan mo rong viet hoa (.JPG / .PNG)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống nhận diện và chấp nhận các đuôi mở rộng viết hoa như .JPG, .PNG mà không báo lỗi định dạng.</t>
+          <t>Verify system nhan dien va chap nhan cac duoi mo rong viet hoa nhu .JPG, .PNG ma khong bao error format.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang mở giao diện tải ảnh đại diện.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang mo interface tai profile photo.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2196,14 +2196,14 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Tải lên tệp tin avatar.JPG (đuôi JPG viết hoa).
-2. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Upload tep tin avatar.JPG (duoi JPG viet hoa).
+2. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống nhận diện .JPG là định dạng hình ảnh hợp lệ.
-Tải ảnh thành công, cập nhật thông tin học sinh bình thường.</t>
+          <t>System nhan dien .JPG la format hinh photo hop le.
+Tai photo successfully, cap nhat thong tin student binh thuong.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 8 - Image File)</t>
+          <t>Related to Validation Rules (Section 8 - Image File)</t>
         </is>
       </c>
     </row>
@@ -2246,19 +2246,19 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Tải lên thất bại do lỗi kết nối Google Drive</t>
+          <t>Upload failed do error ket noi Google Drive</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không lưu link ảnh lỗi và giữ nguyên thông tin học sinh nếu quá trình tải lên Google Drive thất bại.</t>
+          <t>Verify system khong save link photo error va giu nguyen thong tin student neu qua trinh tai len Google Drive failed.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học sinh PNV26003 chưa có ảnh đại diện.
-Đường truyền Google Drive bị ngắt kết nối hoặc lỗi dịch vụ trong lúc tải.</t>
+          <t>User is logged in as Staff.
+Hoc sinh PNV26003 chua co profile photo.
+Duong truyen Google Drive bi ngat ket noi hoac error dich vu trong luc tai.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn học sinh PNV26003 và mở trang Chi tiết Học sinh.
-2. Chọn tải lên file student_avatar3.jpg.
-3. Nhấn "Lưu" (Save).
-4. Quan sát thông báo lỗi và kiểm tra thông tin học sinh.</t>
+          <t>1. Select student PNV26003 va mo trang Chi tiet Hoc sinh.
+2. Select tai len file student_avatar3.jpg.
+3. Nhan "Save" (Save).
+4. Observe notification error va kiem tra thong tin student.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi tải lên (ví dụ: "Upload failed" hoặc "Google Drive unavailable").
-Thông tin học sinh không bị thay đổi, không lưu đường dẫn hỏng (broken link) vào hồ sơ.
-Học sinh vẫn tiếp tục hiển thị avatar mặc định.</t>
+          <t>System display notification error tai len (e.g.: "Upload failed" hoac "Google Drive unavailable").
+Thong tin student khong bi thay doi, khong save duong dan hong (broken link) vao ho so.
+Hoc sinh van tiep tuc display avatar mac dinh.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.5, Error Handling (Mục 9)</t>
+          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2321,18 +2321,18 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Tải lên thất bại do thư mục Google Drive chưa cấu hình</t>
+          <t>Upload failed do thu muc Google Drive chua cau hinh</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hành vi của hệ thống khi cố gắng tải ảnh lên trong khi thư mục Google Drive chưa được thiết lập.</t>
+          <t>Verify hanh vi cua system khi co gang tai photo len trong khi thu muc Google Drive chua duoc thiet lap.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Thư mục lưu trữ Google Drive chưa được cấu hình trong hệ thống.</t>
+          <t>Nguoi dung log in quyen Staff.
+Thu muc archive Google Drive chua duoc cau hinh trong system.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -2342,15 +2342,15 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Mở trang Chi tiết Học sinh PNV26001.
-2. Chọn tải lên file student_avatar.jpg.
-3. Nhấn nút "Lưu" (Save).</t>
+          <t>1. Mo trang Chi tiet Hoc sinh PNV26001.
+2. Select tai len file student_avatar.jpg.
+3. Nhan nut "Save" (Save).</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi cấu hình (ví dụ: "Google Drive folder not configured or unavailable" hoặc "Upload error").
-Quá trình tải lên bị hủy bỏ, thông tin học sinh không bị thay đổi.</t>
+          <t>System display notification error cau hinh (e.g.: "Google Drive folder not configured or unavailable" hoac "Upload error").
+Qua trinh tai len bi huy bo, thong tin student khong bi thay doi.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Error Handling (Mục 9)</t>
+          <t>Related to Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Hiển thị avatar mặc định khi URL ảnh bị lỗi (HTTP 404)</t>
+          <t>Hien thi avatar mac dinh khi URL photo bi error (HTTP 404)</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống tự động phát hiện URL ảnh bị hỏng và chuyển sang hiển thị avatar mặc định.</t>
+          <t>Verify system tu dong phat hien URL photo bi hong va chuyen sang display avatar mac dinh.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Học sinh "Le Thi B" có URL ảnh trong hồ sơ học sinh, nhưng file gốc trên Google Drive đã bị xóa hoặc không truy cập được (lỗi 404).</t>
+          <t>Hoc sinh "Le Thi B" co URL photo trong ho so student, nhung file goc tren Google Drive da bi delete hoac khong access duoc (error 404).</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2413,14 +2413,14 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Đăng nhập hệ thống bằng quyền Staff.
-2. Truy cập danh sách học sinh hoặc chi tiết học sinh "Le Thi B".
-3. Quan sát ảnh đại diện hiển thị.</t>
+          <t>1. Log in system bang quyen Staff.
+2. Truy cap danh sach student hoac chi tiet student "Le Thi B".
+3. Observe profile photo display.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống phát hiện không tải được ảnh từ URL cũ, tự động hiển thị avatar mặc định dạng hình tròn chứa hai chữ cái viết tắt là "LB" mà không cần bất kỳ can thiệp thủ công nào từ người dùng.</t>
+          <t>System phat hien khong tai duoc photo tu URL cu, tu dong display avatar mac format hinh tron chua hai initials la "LB" ma khong can bat ky can thiep thu cong nao tu user.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F04, Rule 5.6, Error Handling (Mục 9)</t>
+          <t>Related to M08-F04, Rule 5.6, Error Handling (Section 9)</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra quyền hạn của Student đối với ảnh đại diện</t>
+          <t>Verify quyen han cua Student for profile photo</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Xác minh tài khoản Student chỉ có quyền xem ảnh đại diện của mình và không có quyền tải lên, chỉnh sửa hoặc xóa ảnh.</t>
+          <t>Verify account Student chi co quyen xem profile photo cua minh va khong co quyen tai len, edit hoac delete photo.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập với quyền Student (email domain @student.passerellesnumeriques.org).</t>
+          <t>Nguoi dung log in voi quyen Student (email domain @student.passerellesnumeriques.org).</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2483,17 +2483,17 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Đăng nhập vào Student Portal.
-2. Truy cập trang thông tin cá nhân.
-3. Kiểm tra sự tồn tại của các nút "Tải ảnh lên" (Upload), "Thay thế" (Replace) hoặc "Xóa ảnh" (Remove).
-4. Thử tìm cách tương tác chỉnh sửa ảnh đại diện.</t>
+          <t>1. Log in vao Student Portal.
+2. Truy cap trang thong tin personal.
+3. Verify su ton tai cua cac nut "Tai photo len" (Upload), "Thay the" (Replace) hoac "Delete photo" (Remove).
+4. Thu tim cach tuong tac edit profile photo.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Học sinh có thể nhìn thấy ảnh đại diện của mình hiển thị ở góc màn hình hoặc trang thông tin.
-Không có nút hoặc tùy chọn nào để tải lên, thay thế hoặc xóa ảnh trên giao diện.
-Trạng thái truy cập hoàn toàn là Chỉ xem (Read-only).</t>
+          <t>Hoc sinh can nhin thay profile photo cua minh display o goc man hinh hoac trang thong tin.
+Khong co nut hoac tuy select nao de tai len, replace hoac delete photo tren interface.
+Status access hoan toan la Chi xem (Read-only).</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M08-F05, Rule 5.1</t>
+          <t>Related to M08-F05, Rule 5.1</t>
         </is>
       </c>
     </row>
@@ -2536,18 +2536,18 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chặn gọi trực tiếp API upload từ tài khoản Student</t>
+          <t>Verify chan goi truc tiep API upload tu account Student</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Xác minh cơ chế bảo mật phía backend từ chối yêu cầu upload/thay thế/xóa ảnh đại diện gửi từ tài khoản Student.</t>
+          <t>Verify co che bao mat phia backend denies requires upload/replace/delete profile photo gui tu account Student.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Student.
-Sử dụng DevTools hoặc công cụ bên thứ ba gửi request trực tiếp đến hàm upload/replace/remove photo của backend.</t>
+          <t>Nguoi dung log in quyen Student.
+Su dung DevTools hoac cong cu ben Tuesday gui request truc tiep den ham upload/replace/remove photo cua backend.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2557,14 +2557,14 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Thực hiện gửi request trực tiếp đến API upload/replace/remove photo sử dụng token/session của Student.
-2. Quan sát phản hồi trả về từ backend.</t>
+          <t>1. Thuc hien gui request truc tiep den API upload/replace/remove photo su dung token/session cua Student.
+2. Observe phan hoi tra ve tu backend.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Backend từ chối yêu cầu, trả về mã lỗi từ chối quyền truy cập (Access Denied / Unauthorized).
-Thông tin ảnh đại diện học sinh không bị ảnh hưởng.</t>
+          <t>Backend denies requires, tra ve ma error denies quyen access (Access Denied / Unauthorized).
+Thong tin profile photo student khong bi photo huong.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2580,11 +2580,11 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 5.1, Error Handling (Mục 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>Related to Rule 5.1, Error Handling (Section 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-M08-019</t>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Từ chối truy cập đối với tài khoản ngoài tổ chức</t>
+          <t>Tu choi access for account external organization</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo người dùng với email không thuộc tổ chức (ví dụ: @gmail.com) không thể truy cập hệ thống và xem ảnh đại diện.</t>
+          <t>Dam bao user voi email khong thuoc organization (e.g.: @gmail.com) cannot access system va xem profile photo.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Người dùng sử dụng tài khoản email cá nhân không phải domain @passerellesnumeriques.org hay @student.passerellesnumeriques.org.</t>
+          <t>Nguoi dung su dung account email personal not domain @passerellesnumeriques.org hay @student.passerellesnumeriques.org.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2627,15 +2627,15 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Mở trình duyệt ẩn danh.
-2. Truy cập URL của hệ thống.
-3. Đăng nhập bằng tài khoản guest_user@gmail.com.</t>
+          <t>1. Mo trinh duyet an danh.
+2. Truy cap URL cua system.
+3. Log in bang account guest_user@gmail.com.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối đăng nhập và chuyển hướng người dùng đến trang "Access Denied" (Từ chối truy cập).
-Không xem được bất cứ thông tin học sinh nào bao gồm cả ảnh đại diện.</t>
+          <t>System denies log in va redirect user den trang "Access Denied" (Tu choi access).
+Khong xem duoc bat cu thong tin student nao bao gom ca profile photo.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Docs - Mục 4 (User Roles) &amp; Mục 6 (Authentication Flow)</t>
+          <t>Related to Docs - Section 4 (User Roles) &amp; Section 6 (Authentication Flow)</t>
         </is>
       </c>
     </row>
@@ -2678,18 +2678,18 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra không tích hợp tính năng chỉnh sửa/cắt ảnh</t>
+          <t>Verify khong tich hop tinh nang edit/cat photo</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Xác minh hệ thống không tích hợp các chức năng chỉnh sửa ảnh, cắt ảnh hoặc xem lịch sử các ảnh đại diện cũ.</t>
+          <t>Verify system khong tich hop cac chuc nang edit photo, cat photo hoac xem lich su cac old profile photo.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đăng nhập quyền Staff.
-Đang trong tiến trình chọn và chuẩn bị tải ảnh lên.</t>
+          <t>Nguoi dung log in quyen Staff.
+Dang trong tien trinh select va chuan bi tai photo len.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -2699,15 +2699,15 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn tải lên file avatar.jpg.
-2. Quan sát các nút và tùy chọn thao tác hiển thị trên giao diện xem trước ảnh.
-3. Kiểm tra xem có chức năng xoay, cắt (crop) hoặc xem danh sách ảnh cũ đã tải lên không.</t>
+          <t>1. Select tai len file avatar.jpg.
+2. Observe cac nut va tuy select thao tac display tren interface xem truoc photo.
+3. Verify whether co chuc nang xoay, cat (crop) hoac xem danh sach old photo da tai len khong.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Giao diện chỉ hiển thị ảnh xem trước đơn giản để người dùng kiểm tra trực quan.
-Không có công cụ chỉnh sửa, cắt ghép hoặc xem lại phiên bản ảnh cũ nào trên hệ thống.</t>
+          <t>Interface chi display preview photo don gian de user kiem tra truc quan.
+Khong co cong cu edit, cat ghep hoac xem lai phien ban old photo nao tren system.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Out of Scope (Mục 13)</t>
+          <t>Related to Out of Scope (Section 13)</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module08_test_cases.xlsx
+++ b/Tests/excel/module08_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module08" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module08'!$A$1:$N$21</definedName>
@@ -401,14 +401,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -432,21 +432,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$13</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$C$9:$C$13</f>
+              <f>'Report'!$C$9:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -459,21 +459,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$13</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$D$9:$D$13</f>
+              <f>'Report'!$D$9:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -486,21 +486,21 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$13</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$E$9:$E$13</f>
+              <f>'Report'!$E$9:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -518,8 +518,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -545,8 +545,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -572,7 +572,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -587,9 +587,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -941,23 +941,23 @@
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="15">
-        <f>COUNTA(A9:A13)</f>
+        <f>COUNTA(A9:A16)</f>
         <v/>
       </c>
       <c r="B5" s="16">
-        <f>F14</f>
+        <f>F17</f>
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>COUNTIF(C9:C13, "&gt;0")</f>
+        <f>COUNTIF(C9:C16, "&gt;0")</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>COUNTIFS(C9:C13, 0, D9:D13, "&gt;0")</f>
+        <f>COUNTIFS(C9:C16, 0, D9:D16, "&gt;0")</f>
         <v/>
       </c>
       <c r="E5" s="19">
-        <f>COUNTIFS(C9:C13, 0, D9:D13, 0, E9:E13, "&gt;0")</f>
+        <f>COUNTIFS(C9:C16, 0, D9:D16, 0, E9:E16, "&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>Photo Replacement</t>
+          <t>Photo Deletion</t>
         </is>
       </c>
       <c r="C10" s="31">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Photo Removal</t>
+          <t>Default Avatar Display</t>
         </is>
       </c>
       <c r="C11" s="25">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Fallback Avatar</t>
+          <t>Avatar Display Sizing</t>
         </is>
       </c>
       <c r="C12" s="31">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Restricted Access</t>
+          <t>Google Drive Storage Naming</t>
         </is>
       </c>
       <c r="C13" s="25">
@@ -1140,30 +1140,114 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>M08-F06</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Drive Integration Error Handling</t>
+        </is>
+      </c>
+      <c r="C14" s="31">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "High")</f>
+        <v/>
+      </c>
+      <c r="D14" s="32">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "Low")</f>
+        <v/>
+      </c>
+      <c r="F14" s="34">
+        <f>SUM(C14:E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>M08-F07</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Role Permissions &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="C15" s="25">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "High")</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "Low")</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>SUM(C15:E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>M08-F08</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Feature Scope Verification</t>
+        </is>
+      </c>
+      <c r="C16" s="31">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "High")</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E16" s="33">
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "Low")</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>SUM(C16:E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="36">
-        <f>COUNTA(A9:A13)&amp;" Features"</f>
-        <v/>
-      </c>
-      <c r="C14" s="35">
-        <f>SUM(C9:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="35">
-        <f>SUM(D9:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="35">
-        <f>SUM(E9:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="35">
-        <f>SUM(F9:F13)</f>
+      <c r="B17" s="36">
+        <f>COUNTA(A9:A16)&amp;" Features"</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>SUM(C9:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>SUM(D9:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>SUM(E9:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>SUM(F9:F16)</f>
         <v/>
       </c>
     </row>
@@ -1270,7 +1354,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="180" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-M08-001</t>
@@ -1278,7 +1362,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1293,40 +1377,36 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Upload valid profile photo in JPG format</t>
+          <t>Upload Valid Profile Photo in JPG Format</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for tai len profile photo format JPG successfully va cap nhat vao thong tin student.</t>
+          <t>Verify functionality for uploading a profile photo in JPG format successfully and updating student details.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Student Detail page of a student without profile photo (displaying default photo).</t>
+Currently on Student Detail page of a student without profile photo (displaying default avatar).</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg (kich thuoc &lt; 2MB)</t>
+          <t>FileName="photo.jpg"; FileType="image/jpeg"; FileSize="1.5MB"</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
-2. Nhap select bieu tuong tai profile photo.
-3. Select file student_avatar.jpg tu thiet bi.
-4. Observe preview photo display tren man hinh.
-5. Nhan nut "Save" (Save).</t>
+          <t>1. Click Upload Photo button;
+2. Select file "photo.jpg";
+3. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>System display notification tai len successfully.
-Anh xem truoc display tuc thi tren interface truoc khi save.
-Sau khi save, thong tin student duoc cap nhat: profile photo display kieu hinh tron tai Sidebar chi tiet (200x200 px) va danh sach student (52x52 px).
-File photo duoc save tren Google Drive duoi ten "Nguyen_Van_A_{Timestamp}.jpg" voi quyen xem "Anyone with the link".</t>
+          <t>Photo uploaded successfully.
+Success notification appears and default avatar is replaced by uploaded JPG photo.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1342,11 +1422,11 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Related to M08-F01, Rule 5.2, Google Drive Integration (Section 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>TC-M08-002</t>
@@ -1354,7 +1434,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1369,12 +1449,12 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Upload valid profile photo in PNG format</t>
+          <t>Upload Valid Profile Photo in PNG Format</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for tai len profile photo format PNG successfully va cap nhat vao thong tin student.</t>
+          <t>Verify functionality for uploading a profile photo in PNG format successfully and updating student details.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -1385,22 +1465,20 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26002; ImageFile=student_avatar2.png</t>
+          <t>FileName="avatar.png"; FileType="image/png"; FileSize="2.0MB"</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Select student PNV26002 va mo trang Chi tiet Hoc sinh.
-2. Nhap select bieu tuong tai profile photo.
-3. Select file student_avatar2.png.
-4. Nhan nut "Save" (Save).</t>
+          <t>1. Click Upload Photo button;
+2. Select file "avatar.png";
+3. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>System display notification tai len successfully.
-Anh dai dien PNG display chinh xac kieu hinh tron o tat ca cac vi tri.
-File photo duoc tai len Google Drive va duoc dat ten theo format {StudentName}_{Timestamp}.jpg.</t>
+          <t>Photo uploaded successfully.
+Default avatar is replaced by uploaded PNG photo.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1416,11 +1494,11 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Related to M08-F01, Rule 5.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="150" customHeight="1">
+          <t>Related Requirement: M08-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-M08-003</t>
@@ -1428,55 +1506,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>M08-F02</t>
+          <t>M08-F01</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Photo Replacement</t>
+          <t>Photo Upload</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Replace current profile photo</t>
+          <t>Replace Current Profile Photo</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Verify khi tai len new profile photo, system tu dong cap nhat thong tin student va delete file old photo tren Google Drive.</t>
+          <t>Verify system overwrites existing photo when uploading a new photo for a student.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Hoc sinh PNV26001 da co san old profile photo tren system va Google Drive.</t>
+Student currently has an existing profile photo.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=new_avatar.jpg</t>
+          <t>NewFileName="new_photo.jpg"</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
-2. Nhap select tai new profile photo.
-3. Select file new_avatar.jpg.
-4. Nhan nut "Save" (Save).
-5. Verify thu muc archive tren Google Drive.</t>
+          <t>1. Click Change Photo button;
+2. Select file "new_photo.jpg";
+3. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>System display notification replace successfully.
-Anh dai dien moi display tren system.
-File old photo cua student PNV26001 tren Google Drive bi delete hoan toan khoi thu muc archive (khong giu lai file cu).
-Chi con lai file new photo tren Google Drive.</t>
+          <t>New photo overwrites old photo successfully on UI and in storage.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1492,11 +1565,11 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Related to M08-F02, Rule 5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1">
+          <t>Related Requirement: M08-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>TC-M08-004</t>
@@ -1504,54 +1577,49 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>M08-F03</t>
+          <t>M08-F02</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Photo Removal</t>
+          <t>Photo Deletion</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Delete current profile photo (Soft Delete)</t>
+          <t>Delete Current Profile Photo (Soft Delete)</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for delete profile photo cua student, chuyen file cu vao Google Drive Trash va display avatar mac dinh.</t>
+          <t>Verify functionality for deleting current photo and reverting student profile to default avatar.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Hoc sinh PNV26001 da co san profile photo tren system.</t>
+Student has an existing profile photo.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001</t>
+          <t>StudentID="ST001"</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Select student PNV26001 va mo trang Chi tiet Hoc sinh.
-2. Nhap select nut "Delete photo" (Remove Photo).
-3. Xac nhan delete khi system display hop thoai xac nhan.
-4. Nhan nut "Save" (Save).
-5. Verify Google Drive Trash.</t>
+          <t>1. Click Delete Photo button;
+2. Confirm deletion in dialog modal.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Anh dai dien cu cua student bi delete khoi interface.
-System display profile photo mac dinh (initials ten student).
-Tren Google Drive, file old photo cua student duoc di chuyen vao trash (Drive Trash) chu khong bi permanently deleted ngay lap tuc.</t>
+          <t>Photo reference is cleared and student avatar reverts to default placeholder avatar.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1567,11 +1635,11 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Related to M08-F03, Rule 5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-M08-005</t>
@@ -1579,52 +1647,49 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>M08-F04</t>
+          <t>M08-F03</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Fallback Avatar</t>
+          <t>Default Avatar Display</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Hien thi avatar mac dinh khi student chua co profile photo</t>
+          <t>Display Default Avatar When Student Has No Profile Photo</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Verify system display profile photo mac dinh la 2 initials cua ten student khi khong co photo.</t>
+          <t>Verify system renders default fallback avatar for students without profile photos.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Hoc sinh "Nguyen Van A" chua tai profile photo len system.</t>
+          <t>User is logged in as Staff or Student.
+Student profile has no photo URL.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>StudentName="Nguyen Van A"</t>
+          <t>PhotoUrl=None</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Vao danh sach student.
-2. Tim student "Nguyen Van A".
-3. Observe profile photo display ben canh ten student.
-4. Verify tai trang Chi tiet student va man hinh Home Dashboard.</t>
+          <t>1. Open Student Detail page;
+2. Observe avatar image element.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>System tu dong display profile photo dang hinh tron chua 2 initials la "NA" (initials cua Ten va Ho).
-Anh mac dinh nay display dong bo o ca danh sach student va chi tiet student.</t>
+          <t>Default SVG/PNG placeholder avatar is rendered cleanly without broken image icon.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1640,11 +1705,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Related to M08-F04, Rule 5.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="135" customHeight="1">
+          <t>Related Requirement: M08-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TC-M08-006</t>
@@ -1652,55 +1717,50 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F04</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Avatar Display Sizing</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Verify kich thuoc display profile photo o cac vi tri khac nhau</t>
+          <t>Verify Profile Photo Rendering Sizes Across Different UI Components</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Verify profile photo display dung kich thuoc cau hinh va dung format hinh tron o moi man hinh.</t>
+          <t>Verify profile photos render with correct circular crop and appropriate dimensions across student list, detail view, and header.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Hoc sinh PNV26001 da co profile photo hop le.</t>
+Student has uploaded profile photo.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001</t>
+          <t>StudentID="ST001"</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Xem photo student tai danh sach student.
-2. Nhap xem chi tiet student PNV26001 va observe Sidebar.
-3. Mo Dialog edit thong tin student.
-4. Ve man hinh Home Dashboard va tim profile photo student do.</t>
+          <t>1. View student photo in Student List table;
+2. View student photo on Student Detail page;
+3. View student avatar in Student Portal header.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Anh dai dien display as hinh tron voi kich thuoc chuan:
-- Danh sach student: 52 x 52 px
-- Dialog edit student: 120 x 120 px
-- Sidebar chi tiet student: 200 x 200 px
-- Home Dashboard: 52 x 52 px</t>
+          <t>Photo scales properly with object-fit: cover, maintains aspect ratio, and clips cleanly to circle without distorting.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1716,11 +1776,11 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Related to Display Locations (Section 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F04, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-M08-007</t>
@@ -1728,7 +1788,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1743,37 +1803,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Nhan Save profile photo khi chua select file photo</t>
+          <t>Click Save Photo Without Selecting Image File</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi user co tinh save photo ma chua select tep tin nao.</t>
+          <t>Verify system blocks submission when Save is clicked without picking an image file.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Dang mo trang Chi tiet Hoc sinh cua mot student chua co photo.</t>
+          <t>User is logged in as Staff.
+Upload modal open.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001</t>
+          <t>SelectedFile=None</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Select student PNV26001.
-2. Kich hoat che do tai profile photo.
-3. Khong select bat ky file nao tu thiet bi.
-4. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
+          <t>1. Open Upload Photo modal;
+2. Click Save Photo button without selecting any file.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>System display cphoto bao error requires select tep tin hinh photo (e.g.: "Image file is required" hoac tuong duong).
-Khong co bat ky thay doi nao duoc thuc hien.</t>
+          <t>System blocks action.
+Validation error appears: "Please select an image file to upload."</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1789,11 +1847,11 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TC-M08-008</t>
@@ -1801,7 +1859,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1816,37 +1874,35 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Upload file not format hinh photo</t>
+          <t>Upload Non-image Format File</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Verify system chan tai len cac tep tin co format is not a photo (nhu .pdf, .docx, .txt).</t>
+          <t>Verify system rejects non-image files (PDF, DOCX, TXT, EXE).</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Staff.
-Dang mo trang Chi tiet Hoc sinh.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; FilePath=document.pdf</t>
+          <t>FileName="document.pdf"</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Select student PNV26001.
-2. Nhap tai profile photo va select file document.pdf.
-3. Nhan nut "Save" (Save) hoac nut xac nhan tai len.</t>
+          <t>1. Click Upload Photo button;
+2. Select file "document.pdf";
+3. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>System khong chap nhan file PDF.
-Hien thi notification error requires tep tin hinh photo hop le (e.g.: "Invalid file format. Please upload JPG or PNG image").
-Khong allows save tep tin nay lam profile photo.</t>
+          <t>System blocks upload.
+Validation error appears: "Invalid file format. Only JPG and PNG image files are allowed."</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1862,11 +1918,11 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="135" customHeight="1">
+          <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-M08-009</t>
@@ -1874,52 +1930,49 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F05</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Google Drive Storage Naming</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Verify cau truc ten file save tren Google Drive</t>
+          <t>Verify File Naming Structure on Google Drive Storage</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Dam bao file photo tai len duoc doi ten theo dung format {StudentName}_{Timestamp}.jpg.</t>
+          <t>Verify system renames uploaded photo files matching student ID format on Google Drive.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Hoc sinh ten "John Smith" chua co photo.</t>
+          <t>User is logged in as Staff.
+Student ID is "ST001".</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>StudentName="John Smith"; ImageFile=avatar.jpg</t>
+          <t>OriginalFile="my_avatar_2026.jpg"; ExpectedStoredFile="ST001.jpg"</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Select student "John Smith" va tai len photo avatar.jpg.
-2. Nhan "Save" (Save).
-3. Log in vao account Google Drive quan tri, mo thu muc archive cau hinh.
-4. Tim kiem file new photo tai len va kiem tra ten file.</t>
+          <t>1. Upload photo "my_avatar_2026.jpg" for student ST001;
+2. Inspect saved file name in Google Drive directory.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>File photo duoc archive tren Google Drive co ten chinh xac la "John_Smith_YYYYMMDDHHMMSS.jpg" (trong do YYYYMMDDHHMMSS la period luc tai len).
-Dinh dang file duoc chuan hoa thanh duoi mo rong .jpg.</t>
+          <t>File is saved to Google Drive with standardized filename format "ST001.jpg".</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -1928,18 +1981,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>TC-M08-010</t>
@@ -1947,51 +2000,49 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F05</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Google Drive Storage Naming</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Upload photo cho student co ten chua ky tu tieng Viet co dau</t>
+          <t>Upload Photo for Student with Special Characters in Original Filename</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Verify whether ten file tren Google Drive co duoc xu ly chuan hoa ky tu tieng Viet co dau va khoang trang hay khong.</t>
+          <t>Verify uploading files with non-ASCII or special characters in filename renames safely during storage.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Co student ten "Nguyen Hoang Nam".</t>
+          <t>User is logged in as Staff.
+Student ID is "ST002".</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyen Hoang Nam"; ImageFile=avatar.jpg</t>
+          <t>OriginalFile="avatar_special_char_2026.png"; ExpectedStoredFile="ST002.png"</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Mo trang chi tiet student "Nguyen Hoang Nam" va tai len profile photo.
-2. Nhan "Save".
-3. Mo Google Drive kiem tra ten file photo vua create.</t>
+          <t>1. Select file with Unicode filename "avatar_special_char_2026.png";
+2. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>File photo duoc tai len successfully.
-Ten file tren Google Drive duoc chuan hoa (e.g. chuyen thanh "Nguyen_Hoang_Nam_{Timestamp}.jpg" hoac giu nguyen ky tu tieng Viet co dau nhung khoang trang thay bang gach duoi va khong bi error display/ma hoa ky tu).</t>
+          <t>File uploads cleanly and renames to "ST002.png" without encoding errors.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2007,11 +2058,11 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>Related Requirement: M08-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-M08-011</t>
@@ -2019,50 +2070,48 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F05</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Google Drive Storage Naming</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Verify quyen access tep tin (File Permission) tren Google Drive</t>
+          <t>Verify File Permissions on Google Drive Storage</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Dam bao tep tin photo tai len duoc cau hinh quyen chia se cong khai o che do chi xem de system display duoc.</t>
+          <t>Verify uploaded photo files on Google Drive are configured with public read permission for rendering.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Tai photo len cho student PNV26001 successfully.</t>
+          <t>Photo uploaded to Google Drive.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001</t>
+          <t>FileId="1A2B3C"</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Mo account Google Drive quan tri, tim file photo cua student PNV26001 vua tai len.
-2. Nhap chuot phai select "Chia se" (Share) -&gt; "Nhan lien ket" (Get link).
-3. Verify cai dat quyen access chung.</t>
+          <t>1. Upload photo for student;
+2. Verify direct view URL accessibility.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Quyen access chung cua file duoc thiet lap la "Bat ky ai co lien ket nay" (Anyone with the link) va vai tro duoc gan la "Nguoi xem" (Viewer / View only).</t>
+          <t>Image URL resolves and renders image in web browser without authentication wall.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2078,11 +2127,11 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Related to Storage Information (Section 3), Google Drive Integration (Section 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+          <t>Related Requirement: M08-F05, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TC-M08-012</t>
@@ -2090,7 +2139,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2105,34 +2154,34 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Upload photo co size lon</t>
+          <t>Upload Oversized Image File Exceeding Maximum Limit</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Verify phan hoi cua system khi co gang tai len mot hinh photo co kich thuoc tep tin lon.</t>
+          <t>Verify system blocks uploading files exceeding file size limit (e.g., &gt; 5MB).</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Dang mo interface tai profile photo.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=large_photo.jpg (size 15MB)</t>
+          <t>FileName="large_photo.jpg"; FileSize="12MB"</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Upload tep tin large_photo.jpg size 15MB.
-2. Nhan nut "Save" (Save).</t>
+          <t>1. Select oversized file "large_photo.jpg" (12MB);
+2. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>System tai len successfully neu khong cau hinh gioi han kich thuoc, HOAC neu system co gioi han size: display notification error requires photo nho hon muc quy dinh (e.g.: "File size exceeds limit") va ngan khong cho tai len.</t>
+          <t>System blocks upload.
+Validation error appears: "File size exceeds maximum limit of 5MB."</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2141,18 +2190,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Related to Test Data Preparation (Section 11 - Large image)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-M08-013</t>
@@ -2160,7 +2209,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2175,35 +2224,33 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Upload hinh photo co phan mo rong viet hoa (.JPG / .PNG)</t>
+          <t>Upload Image File with Uppercase Extension (.JPG / .PNG)</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Verify system nhan dien va chap nhan cac duoi mo rong viet hoa nhu .JPG, .PNG ma khong bao error format.</t>
+          <t>Verify system handles uppercase file extensions (.JPG, .PNG) correctly.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Dang mo interface tai profile photo.</t>
+          <t>User is logged in as Staff.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=avatar.JPG</t>
+          <t>FileName="PHOTO.JPG"</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Upload tep tin avatar.JPG (duoi JPG viet hoa).
-2. Nhan nut "Save" (Save).</t>
+          <t>1. Select file "PHOTO.JPG";
+2. Click Save Photo button.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>System nhan dien .JPG la format hinh photo hop le.
-Tai photo successfully, cap nhat thong tin student binh thuong.</t>
+          <t>System accepts upload successfully regardless of extension case.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2219,11 +2266,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 8 - Image File)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TC-M08-014</t>
@@ -2231,54 +2278,49 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F06</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Drive Integration Error Handling</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Upload failed do error ket noi Google Drive</t>
+          <t>Upload Fails Due to Google Drive Connection Error</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong save link photo error va giu nguyen thong tin student neu qua trinh tai len Google Drive failed.</t>
+          <t>Verify graceful error handling when Google Drive API connection fails.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Hoc sinh PNV26003 chua co profile photo.
-Duong truyen Google Drive bi ngat ket noi hoac error dich vu trong luc tai.</t>
+Google Drive service is disconnected or unreachable.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26003; ImageFile=student_avatar3.jpg</t>
+          <t>DriveApiStatus="Disconnected"</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Select student PNV26003 va mo trang Chi tiet Hoc sinh.
-2. Select tai len file student_avatar3.jpg.
-3. Nhan "Save" (Save).
-4. Observe notification error va kiem tra thong tin student.</t>
+          <t>1. Attempt to upload profile photo when Drive API is offline.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>System display notification error tai len (e.g.: "Upload failed" hoac "Google Drive unavailable").
-Thong tin student khong bi thay doi, khong save duong dan hong (broken link) vao ho so.
-Hoc sinh van tiep tuc display avatar mac dinh.</t>
+          <t>System catches exception.
+Error message displays: "Unable to connect to storage service. Please try again later."</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2287,18 +2329,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 5.5, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
+          <t>Related Requirement: M08-F06, Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-M08-015</t>
@@ -2306,51 +2348,48 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F06</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Drive Integration Error Handling</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Upload failed do thu muc Google Drive chua cau hinh</t>
+          <t>Upload Fails Due to Unconfigured Google Drive Target Folder</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Verify hanh vi cua system khi co gang tai photo len trong khi thu muc Google Drive chua duoc thiet lap.</t>
+          <t>Verify error notification when Drive folder ID is missing or invalid in system settings.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Thu muc archive Google Drive chua duoc cau hinh trong system.</t>
+          <t>User is logged in as Staff.
+Target folder ID in config is invalid.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=student_avatar.jpg</t>
+          <t>DriveFolderId="INVALID_ID"</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Mo trang Chi tiet Hoc sinh PNV26001.
-2. Select tai len file student_avatar.jpg.
-3. Nhan nut "Save" (Save).</t>
+          <t>1. Attempt to upload profile photo.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>System display notification error cau hinh (e.g.: "Google Drive folder not configured or unavailable" hoac "Upload error").
-Qua trinh tai len bi huy bo, thong tin student khong bi thay doi.</t>
+          <t>System blocks upload and logs configuration error message for administrator.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2366,11 +2405,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Related to Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Related Requirement: M08-F06, Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M08-016</t>
@@ -2378,49 +2417,49 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>M08-F04</t>
+          <t>M08-F03</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Fallback Avatar</t>
+          <t>Default Avatar Display</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Hien thi avatar mac dinh khi URL photo bi error (HTTP 404)</t>
+          <t>Display Default Avatar When Photo URL Returns HTTP 404 Error</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Verify system tu dong phat hien URL photo bi hong va chuyen sang display avatar mac dinh.</t>
+          <t>Verify system gracefully falls back to default avatar if image URL fails to load (404 error).</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Hoc sinh "Le Thi B" co URL photo trong ho so student, nhung file goc tren Google Drive da bi delete hoac khong access duoc (error 404).</t>
+          <t>User is logged in.
+Student photo URL in database points to non-existent image resource.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Le Thi B"</t>
+          <t>PhotoUrl="https://drive.google.com/non_existent.jpg"</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Log in system bang quyen Staff.
-2. Truy cap danh sach student hoac chi tiet student "Le Thi B".
-3. Observe profile photo display.</t>
+          <t>1. Open Student Detail page;
+2. Observe image element on error event.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>System phat hien khong tai duoc photo tu URL cu, tu dong display avatar mac format hinh tron chua hai initials la "LB" ma khong can bat ky can thiep thu cong nao tu user.</t>
+          <t>Image onError handler triggers and smoothly replaces broken image link with default placeholder avatar.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2429,18 +2468,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Related to M08-F04, Rule 5.6, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="135" customHeight="1">
+          <t>Related Requirement: M08-F03, Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-M08-017</t>
@@ -2448,52 +2487,48 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>M08-F05</t>
+          <t>M08-F07</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Restricted Access</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Verify quyen han cua Student for profile photo</t>
+          <t>Verify Student Role Cannot Upload or Delete Profile Photo</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Verify account Student chi co quyen xem profile photo cua minh va khong co quyen tai len, edit hoac delete photo.</t>
+          <t>Verify Student role has read-only photo permissions and cannot upload or delete photos.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung log in voi quyen Student (email domain @student.passerellesnumeriques.org).</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>StudentAccount=student01@student.passerellesnumeriques.org</t>
+          <t>StudentEmail="student@student.passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Log in vao Student Portal.
-2. Truy cap trang thong tin personal.
-3. Verify su ton tai cua cac nut "Tai photo len" (Upload), "Thay the" (Replace) hoac "Delete photo" (Remove).
-4. Thu tim cach tuong tac edit profile photo.</t>
+          <t>1. Navigate to Student Detail / Profile page as Student;
+2. Inspect photo options.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Hoc sinh can nhin thay profile photo cua minh display o goc man hinh hoac trang thong tin.
-Khong co nut hoac tuy select nao de tai len, replace hoac delete photo tren interface.
-Status access hoan toan la Chi xem (Read-only).</t>
+          <t>Upload Photo and Delete Photo buttons are absent from UI.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2509,11 +2544,11 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Related to M08-F05, Rule 5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="75" customHeight="1">
+          <t>Related Requirement: M08-F07, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TC-M08-018</t>
@@ -2521,50 +2556,47 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>M08-F05</t>
+          <t>M08-F07</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Restricted Access</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Verify chan goi truc tiep API upload tu account Student</t>
+          <t>Block Direct API Calls for Photo Upload from Student Account</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Verify co che bao mat phia backend denies requires upload/replace/delete profile photo gui tu account Student.</t>
+          <t>Verify backend API blocks photo upload requests submitted with Student JWT authorization token.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Student.
-Su dung DevTools hoac cong cu ben Tuesday gui request truc tiep den ham upload/replace/remove photo cua backend.</t>
+          <t>Student authorization token.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>StudentAccount=student01@student.passerellesnumeriques.org</t>
+          <t>ApiEndpoint="POST /api/students/st001/photo"</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Thuc hien gui request truc tiep den API upload/replace/remove photo su dung token/session cua Student.
-2. Observe phan hoi tra ve tu backend.</t>
+          <t>1. Submit direct HTTP POST upload request using Student auth token.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Backend denies requires, tra ve ma error denies quyen access (Access Denied / Unauthorized).
-Thong tin profile photo student khong bi photo huong.</t>
+          <t>Backend rejects request with HTTP 403 Forbidden status.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2580,11 +2612,11 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 5.1, Error Handling (Section 9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="75" customHeight="1">
+          <t>Related Requirement: M08-F07, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-M08-019</t>
@@ -2592,50 +2624,47 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>M08-F05</t>
+          <t>M08-F07</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Restricted Access</t>
+          <t>Role Permissions &amp; Access Control</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Tu choi access for account external organization</t>
+          <t>Deny Access to External Organization Accounts</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Dam bao user voi email khong thuoc organization (e.g.: @gmail.com) cannot access system va xem profile photo.</t>
+          <t>Verify users from external email domains cannot access profile photo API or management UI.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Nguoi dung su dung account email personal not domain @passerellesnumeriques.org hay @student.passerellesnumeriques.org.</t>
+          <t>External domain account.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>UserEmail=guest_user@gmail.com</t>
+          <t>UserEmail="external@gmail.com"</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Mo trinh duyet an danh.
-2. Truy cap URL cua system.
-3. Log in bang account guest_user@gmail.com.</t>
+          <t>1. Attempt access with external account.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>System denies log in va redirect user den trang "Access Denied" (Tu choi access).
-Khong xem duoc bat cu thong tin student nao bao gom ca profile photo.</t>
+          <t>System denies access with HTTP 403 Forbidden.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2651,11 +2680,11 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Related to Docs - Section 4 (User Roles) &amp; Section 6 (Authentication Flow)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="120" customHeight="1">
+          <t>Related Requirement: M08-F07, User Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TC-M08-020</t>
@@ -2663,51 +2692,49 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Module 08 – Profile Photo Management</t>
+          <t>Module 08 - Profile Photo Management</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>M08-F01</t>
+          <t>M08-F08</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Photo Upload</t>
+          <t>Feature Scope Verification</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Verify khong tich hop tinh nang edit/cat photo</t>
+          <t>Verify Image Editing and Cropping Features Are Not Present</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Verify system khong tich hop cac chuc nang edit photo, cat photo hoac xem lich su cac old profile photo.</t>
+          <t>Verify profile photo management upload directly stores selected file without client-side image cropping tools.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung log in quyen Staff.
-Dang trong tien trinh select va chuan bi tai photo len.</t>
+          <t>User is logged in as Staff.
+Uploading photo.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>StudentCode=PNV26001; ImageFile=avatar.jpg</t>
+          <t>FileName="photo.jpg"</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Select tai len file avatar.jpg.
-2. Observe cac nut va tuy select thao tac display tren interface xem truoc photo.
-3. Verify whether co chuc nang xoay, cat (crop) hoac xem danh sach old photo da tai len khong.</t>
+          <t>1. Select image file in upload modal;
+2. Observe upload workflow.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Interface chi display preview photo don gian de user kiem tra truc quan.
-Khong co cong cu edit, cat ghep hoac xem lai phien ban old photo nao tren system.</t>
+          <t>File uploads directly without displaying cropping modal, maintaining simple out-of-scope workflow.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2723,7 +2750,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Related to Out of Scope (Section 13)</t>
+          <t>Related Requirement: M08-F08, Out of Scope (Section 12)</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module08_test_cases.xlsx
+++ b/Tests/excel/module08_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module08" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module08'!$A$1:$N$21</definedName>
@@ -401,14 +401,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -432,10 +432,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -459,10 +459,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -486,10 +486,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -518,8 +518,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -545,8 +545,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -572,7 +572,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -587,9 +587,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module08_test_cases.xlsx
+++ b/Tests/excel/module08_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module08" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module08'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module08'!$A$1:$O$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1012,15 +1012,15 @@
         </is>
       </c>
       <c r="C9" s="25">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="27">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A9, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="28">
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="C10" s="31">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D10" s="32">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="33">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A10, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="34">
@@ -1068,15 +1068,15 @@
         </is>
       </c>
       <c r="C11" s="25">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D11" s="26">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="27">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A11, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="28">
@@ -1096,15 +1096,15 @@
         </is>
       </c>
       <c r="C12" s="31">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="33">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A12, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="34">
@@ -1124,15 +1124,15 @@
         </is>
       </c>
       <c r="C13" s="25">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D13" s="26">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="27">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A13, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="28">
@@ -1152,15 +1152,15 @@
         </is>
       </c>
       <c r="C14" s="31">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D14" s="32">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A14, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="34">
@@ -1180,15 +1180,15 @@
         </is>
       </c>
       <c r="C15" s="25">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D15" s="26">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A15, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="28">
@@ -1208,15 +1208,15 @@
         </is>
       </c>
       <c r="C16" s="31">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "High")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$N$2:$N$21, "High")</f>
         <v/>
       </c>
       <c r="D16" s="32">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "Medium")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$N$2:$N$21, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$M$2:$M$21, "Low")</f>
+        <f>COUNTIFS('Module08'!$C$2:$C$21, A16, 'Module08'!$N$2:$N$21, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="34">
@@ -1263,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1278,8 +1278,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1345,10 +1346,15 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1415,12 +1421,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Business Rules 6.1</t>
         </is>
@@ -1487,12 +1494,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Business Rules 6.1</t>
         </is>
@@ -1558,12 +1566,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Business Rules 6.1</t>
         </is>
@@ -1628,12 +1637,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F02, Business Rules 6.2</t>
         </is>
@@ -1698,12 +1708,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F03, Business Rules 6.3</t>
         </is>
@@ -1769,12 +1780,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F04, UI Standards</t>
         </is>
@@ -1840,12 +1852,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
         </is>
@@ -1911,12 +1924,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
         </is>
@@ -1981,12 +1995,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F05, Business Rules 6.5</t>
         </is>
@@ -2051,12 +2066,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F05, Business Rules 6.5</t>
         </is>
@@ -2120,12 +2136,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F05, Business Rules 6.5</t>
         </is>
@@ -2190,12 +2207,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Validation Rules (Section 8)</t>
         </is>
@@ -2259,12 +2277,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F01, Business Rules 6.1</t>
         </is>
@@ -2329,12 +2348,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F06, Error Handling (Section 8)</t>
         </is>
@@ -2398,12 +2418,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F06, Error Handling (Section 8)</t>
         </is>
@@ -2468,12 +2489,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F03, Error Handling (Section 8)</t>
         </is>
@@ -2537,12 +2559,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F07, User Roles</t>
         </is>
@@ -2605,12 +2628,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F07, User Roles</t>
         </is>
@@ -2673,12 +2697,13 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F07, User Roles</t>
         </is>
@@ -2743,24 +2768,25 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M08-F08, Out of Scope (Section 12)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N21"/>
+  <autoFilter ref="A1:O21"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="N2:N121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
